--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 бррсч ост ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\14,09,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E177E366-79B2-417C-85D2-3F24244CBF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4110C5EE-4F35-4230-B0CA-ABB486C2B6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$119</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -6673,7 +6673,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AY494"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6927,7 +6926,7 @@
       <c r="AX3" s="5"/>
       <c r="AY3" s="5"/>
     </row>
-    <row r="4" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -7138,7 +7137,7 @@
       <c r="AX5" s="5"/>
       <c r="AY5" s="5"/>
     </row>
-    <row r="6" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>37</v>
       </c>
@@ -7265,7 +7264,7 @@
       <c r="AX6" s="5"/>
       <c r="AY6" s="5"/>
     </row>
-    <row r="7" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>40</v>
       </c>
@@ -7524,7 +7523,7 @@
       <c r="AX8" s="5"/>
       <c r="AY8" s="5"/>
     </row>
-    <row r="9" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>44</v>
       </c>
@@ -7782,7 +7781,7 @@
       <c r="AX10" s="5"/>
       <c r="AY10" s="5"/>
     </row>
-    <row r="11" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
@@ -7906,7 +7905,7 @@
       <c r="AX11" s="5"/>
       <c r="AY11" s="5"/>
     </row>
-    <row r="12" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -8162,7 +8161,7 @@
       <c r="AX13" s="5"/>
       <c r="AY13" s="5"/>
     </row>
-    <row r="14" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>50</v>
       </c>
@@ -8423,7 +8422,7 @@
       <c r="AX15" s="5"/>
       <c r="AY15" s="5"/>
     </row>
-    <row r="16" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>52</v>
       </c>
@@ -8550,7 +8549,7 @@
       <c r="AX16" s="5"/>
       <c r="AY16" s="5"/>
     </row>
-    <row r="17" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>53</v>
       </c>
@@ -8678,7 +8677,7 @@
       <c r="AX17" s="5"/>
       <c r="AY17" s="5"/>
     </row>
-    <row r="18" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>54</v>
       </c>
@@ -8803,7 +8802,7 @@
       <c r="AX18" s="5"/>
       <c r="AY18" s="5"/>
     </row>
-    <row r="19" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>55</v>
       </c>
@@ -9061,7 +9060,7 @@
       <c r="AX20" s="5"/>
       <c r="AY20" s="5"/>
     </row>
-    <row r="21" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>57</v>
       </c>
@@ -9187,7 +9186,7 @@
       <c r="AX21" s="5"/>
       <c r="AY21" s="5"/>
     </row>
-    <row r="22" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>58</v>
       </c>
@@ -9319,7 +9318,7 @@
       <c r="AX22" s="5"/>
       <c r="AY22" s="5"/>
     </row>
-    <row r="23" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>59</v>
       </c>
@@ -9445,7 +9444,7 @@
       <c r="AX23" s="5"/>
       <c r="AY23" s="5"/>
     </row>
-    <row r="24" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>61</v>
       </c>
@@ -9561,7 +9560,7 @@
       <c r="AX24" s="5"/>
       <c r="AY24" s="5"/>
     </row>
-    <row r="25" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>64</v>
       </c>
@@ -9683,7 +9682,7 @@
       <c r="AX25" s="5"/>
       <c r="AY25" s="5"/>
     </row>
-    <row r="26" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>65</v>
       </c>
@@ -9808,7 +9807,7 @@
       <c r="AX26" s="5"/>
       <c r="AY26" s="5"/>
     </row>
-    <row r="27" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>66</v>
       </c>
@@ -9928,7 +9927,7 @@
       <c r="AX27" s="5"/>
       <c r="AY27" s="5"/>
     </row>
-    <row r="28" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>67</v>
       </c>
@@ -10053,7 +10052,7 @@
       <c r="AX28" s="5"/>
       <c r="AY28" s="5"/>
     </row>
-    <row r="29" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>68</v>
       </c>
@@ -10309,7 +10308,7 @@
       <c r="AX30" s="5"/>
       <c r="AY30" s="5"/>
     </row>
-    <row r="31" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>71</v>
       </c>
@@ -10436,7 +10435,7 @@
       <c r="AX31" s="5"/>
       <c r="AY31" s="5"/>
     </row>
-    <row r="32" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>72</v>
       </c>
@@ -10566,7 +10565,7 @@
       <c r="AX32" s="5"/>
       <c r="AY32" s="5"/>
     </row>
-    <row r="33" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>73</v>
       </c>
@@ -10682,7 +10681,7 @@
       <c r="AX33" s="5"/>
       <c r="AY33" s="5"/>
     </row>
-    <row r="34" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>75</v>
       </c>
@@ -10808,7 +10807,7 @@
       <c r="AX34" s="5"/>
       <c r="AY34" s="5"/>
     </row>
-    <row r="35" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>76</v>
       </c>
@@ -10932,7 +10931,7 @@
       <c r="AX35" s="5"/>
       <c r="AY35" s="5"/>
     </row>
-    <row r="36" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>79</v>
       </c>
@@ -11304,7 +11303,7 @@
       <c r="AX38" s="5"/>
       <c r="AY38" s="5"/>
     </row>
-    <row r="39" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>84</v>
       </c>
@@ -11564,7 +11563,7 @@
       <c r="AX40" s="5"/>
       <c r="AY40" s="5"/>
     </row>
-    <row r="41" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>86</v>
       </c>
@@ -11822,7 +11821,7 @@
       <c r="AX42" s="5"/>
       <c r="AY42" s="5"/>
     </row>
-    <row r="43" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>88</v>
       </c>
@@ -12340,7 +12339,7 @@
       <c r="AX46" s="5"/>
       <c r="AY46" s="5"/>
     </row>
-    <row r="47" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>93</v>
       </c>
@@ -12734,7 +12733,7 @@
       <c r="AX49" s="5"/>
       <c r="AY49" s="5"/>
     </row>
-    <row r="50" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>96</v>
       </c>
@@ -12852,7 +12851,7 @@
       <c r="AX50" s="5"/>
       <c r="AY50" s="5"/>
     </row>
-    <row r="51" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>97</v>
       </c>
@@ -12976,7 +12975,7 @@
       <c r="AX51" s="5"/>
       <c r="AY51" s="5"/>
     </row>
-    <row r="52" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>99</v>
       </c>
@@ -13235,7 +13234,7 @@
       <c r="AX53" s="5"/>
       <c r="AY53" s="5"/>
     </row>
-    <row r="54" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>102</v>
       </c>
@@ -13360,7 +13359,7 @@
       <c r="AX54" s="5"/>
       <c r="AY54" s="5"/>
     </row>
-    <row r="55" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>104</v>
       </c>
@@ -13614,7 +13613,7 @@
       <c r="AX56" s="5"/>
       <c r="AY56" s="5"/>
     </row>
-    <row r="57" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>106</v>
       </c>
@@ -13843,7 +13842,7 @@
         <v>13.7</v>
       </c>
       <c r="AK58" s="18">
-        <f t="shared" ref="AK58:AK59" si="26">I58</f>
+        <f t="shared" ref="AK58" si="26">I58</f>
         <v>1</v>
       </c>
       <c r="AL58" s="5">
@@ -13993,7 +13992,7 @@
       <c r="AX59" s="5"/>
       <c r="AY59" s="5"/>
     </row>
-    <row r="60" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>110</v>
       </c>
@@ -14118,7 +14117,7 @@
       <c r="AX60" s="5"/>
       <c r="AY60" s="5"/>
     </row>
-    <row r="61" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>112</v>
       </c>
@@ -14238,7 +14237,7 @@
       <c r="AX61" s="5"/>
       <c r="AY61" s="5"/>
     </row>
-    <row r="62" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>113</v>
       </c>
@@ -14362,7 +14361,7 @@
       <c r="AX62" s="5"/>
       <c r="AY62" s="5"/>
     </row>
-    <row r="63" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>114</v>
       </c>
@@ -14484,7 +14483,7 @@
       <c r="AX63" s="5"/>
       <c r="AY63" s="5"/>
     </row>
-    <row r="64" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>115</v>
       </c>
@@ -14609,7 +14608,7 @@
       <c r="AX64" s="5"/>
       <c r="AY64" s="5"/>
     </row>
-    <row r="65" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>116</v>
       </c>
@@ -15139,7 +15138,7 @@
       <c r="AX68" s="5"/>
       <c r="AY68" s="5"/>
     </row>
-    <row r="69" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>120</v>
       </c>
@@ -15395,7 +15394,7 @@
       <c r="AX70" s="5"/>
       <c r="AY70" s="5"/>
     </row>
-    <row r="71" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>122</v>
       </c>
@@ -15517,7 +15516,7 @@
       <c r="AX71" s="5"/>
       <c r="AY71" s="5"/>
     </row>
-    <row r="72" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>123</v>
       </c>
@@ -15642,7 +15641,7 @@
       <c r="AX72" s="5"/>
       <c r="AY72" s="5"/>
     </row>
-    <row r="73" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>124</v>
       </c>
@@ -15767,7 +15766,7 @@
       <c r="AX73" s="5"/>
       <c r="AY73" s="5"/>
     </row>
-    <row r="74" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>125</v>
       </c>
@@ -15885,7 +15884,7 @@
       <c r="AX74" s="5"/>
       <c r="AY74" s="5"/>
     </row>
-    <row r="75" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>126</v>
       </c>
@@ -16138,7 +16137,7 @@
       <c r="AX76" s="5"/>
       <c r="AY76" s="5"/>
     </row>
-    <row r="77" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>127</v>
       </c>
@@ -16367,7 +16366,7 @@
         <v>31.833199999999998</v>
       </c>
       <c r="AK78" s="18">
-        <f t="shared" ref="AK78:AK81" si="42">I78</f>
+        <f t="shared" ref="AK78:AK80" si="42">I78</f>
         <v>1</v>
       </c>
       <c r="AL78" s="5">
@@ -16795,7 +16794,7 @@
       <c r="AX81" s="5"/>
       <c r="AY81" s="5"/>
     </row>
-    <row r="82" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>132</v>
       </c>
@@ -16922,7 +16921,7 @@
       <c r="AX82" s="5"/>
       <c r="AY82" s="5"/>
     </row>
-    <row r="83" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>133</v>
       </c>
@@ -17044,7 +17043,7 @@
       <c r="AX83" s="5"/>
       <c r="AY83" s="5"/>
     </row>
-    <row r="84" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>134</v>
       </c>
@@ -17166,7 +17165,7 @@
       <c r="AX84" s="5"/>
       <c r="AY84" s="5"/>
     </row>
-    <row r="85" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>135</v>
       </c>
@@ -17293,7 +17292,7 @@
       <c r="AX85" s="5"/>
       <c r="AY85" s="5"/>
     </row>
-    <row r="86" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>136</v>
       </c>
@@ -17411,7 +17410,7 @@
       <c r="AX86" s="5"/>
       <c r="AY86" s="5"/>
     </row>
-    <row r="87" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>137</v>
       </c>
@@ -17667,7 +17666,7 @@
       <c r="AX88" s="5"/>
       <c r="AY88" s="5"/>
     </row>
-    <row r="89" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>139</v>
       </c>
@@ -17785,7 +17784,7 @@
       <c r="AX89" s="5"/>
       <c r="AY89" s="5"/>
     </row>
-    <row r="90" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>141</v>
       </c>
@@ -17912,7 +17911,7 @@
       <c r="AX90" s="5"/>
       <c r="AY90" s="5"/>
     </row>
-    <row r="91" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>142</v>
       </c>
@@ -18034,7 +18033,7 @@
       <c r="AX91" s="5"/>
       <c r="AY91" s="5"/>
     </row>
-    <row r="92" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>143</v>
       </c>
@@ -18150,7 +18149,7 @@
       <c r="AX92" s="5"/>
       <c r="AY92" s="5"/>
     </row>
-    <row r="93" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>144</v>
       </c>
@@ -18272,7 +18271,7 @@
       <c r="AX93" s="5"/>
       <c r="AY93" s="5"/>
     </row>
-    <row r="94" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>146</v>
       </c>
@@ -18394,7 +18393,7 @@
       <c r="AX94" s="5"/>
       <c r="AY94" s="5"/>
     </row>
-    <row r="95" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>147</v>
       </c>
@@ -18516,7 +18515,7 @@
       <c r="AX95" s="5"/>
       <c r="AY95" s="5"/>
     </row>
-    <row r="96" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>148</v>
       </c>
@@ -18642,7 +18641,7 @@
       <c r="AX96" s="5"/>
       <c r="AY96" s="5"/>
     </row>
-    <row r="97" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>149</v>
       </c>
@@ -18766,7 +18765,7 @@
       <c r="AX97" s="5"/>
       <c r="AY97" s="5"/>
     </row>
-    <row r="98" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>140</v>
       </c>
@@ -18892,7 +18891,7 @@
       <c r="AX98" s="5"/>
       <c r="AY98" s="5"/>
     </row>
-    <row r="99" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>150</v>
       </c>
@@ -19021,7 +19020,7 @@
       <c r="AX99" s="5"/>
       <c r="AY99" s="5"/>
     </row>
-    <row r="100" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>151</v>
       </c>
@@ -19147,7 +19146,7 @@
       <c r="AX100" s="5"/>
       <c r="AY100" s="5"/>
     </row>
-    <row r="101" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>152</v>
       </c>
@@ -19270,7 +19269,7 @@
       <c r="AX101" s="5"/>
       <c r="AY101" s="5"/>
     </row>
-    <row r="102" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>153</v>
       </c>
@@ -19396,7 +19395,7 @@
       <c r="AX102" s="5"/>
       <c r="AY102" s="5"/>
     </row>
-    <row r="103" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>154</v>
       </c>
@@ -19519,7 +19518,7 @@
       <c r="AX103" s="5"/>
       <c r="AY103" s="5"/>
     </row>
-    <row r="104" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>155</v>
       </c>
@@ -19776,7 +19775,7 @@
       <c r="AX105" s="5"/>
       <c r="AY105" s="5"/>
     </row>
-    <row r="106" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>158</v>
       </c>
@@ -19900,7 +19899,7 @@
       <c r="AX106" s="5"/>
       <c r="AY106" s="5"/>
     </row>
-    <row r="107" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>159</v>
       </c>
@@ -20025,7 +20024,7 @@
       <c r="AX107" s="5"/>
       <c r="AY107" s="5"/>
     </row>
-    <row r="108" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>160</v>
       </c>
@@ -20145,7 +20144,7 @@
       <c r="AX108" s="5"/>
       <c r="AY108" s="5"/>
     </row>
-    <row r="109" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>162</v>
       </c>
@@ -20269,7 +20268,7 @@
       <c r="AX109" s="5"/>
       <c r="AY109" s="5"/>
     </row>
-    <row r="110" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>163</v>
       </c>
@@ -20389,7 +20388,7 @@
       <c r="AX110" s="5"/>
       <c r="AY110" s="5"/>
     </row>
-    <row r="111" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>164</v>
       </c>
@@ -20513,7 +20512,7 @@
       <c r="AX111" s="5"/>
       <c r="AY111" s="5"/>
     </row>
-    <row r="112" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>166</v>
       </c>
@@ -20640,7 +20639,7 @@
       <c r="AX112" s="5"/>
       <c r="AY112" s="5"/>
     </row>
-    <row r="113" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>80</v>
       </c>
@@ -20768,7 +20767,7 @@
       <c r="AX113" s="5"/>
       <c r="AY113" s="5"/>
     </row>
-    <row r="114" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>169</v>
       </c>
@@ -20882,7 +20881,7 @@
       <c r="AX114" s="5"/>
       <c r="AY114" s="5"/>
     </row>
-    <row r="115" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>170</v>
       </c>
@@ -21009,7 +21008,7 @@
       <c r="AX115" s="5"/>
       <c r="AY115" s="5"/>
     </row>
-    <row r="116" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>172</v>
       </c>
@@ -21131,7 +21130,7 @@
       <c r="AX116" s="5"/>
       <c r="AY116" s="5"/>
     </row>
-    <row r="117" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>173</v>
       </c>
@@ -21253,7 +21252,7 @@
       <c r="AX117" s="5"/>
       <c r="AY117" s="5"/>
     </row>
-    <row r="118" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>174</v>
       </c>
@@ -21375,7 +21374,7 @@
       <c r="AX118" s="5"/>
       <c r="AY118" s="5"/>
     </row>
-    <row r="119" spans="1:51" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>175</v>
       </c>
@@ -41363,13 +41362,7 @@
       <c r="AY494" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AI119" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AI119" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
